--- a/artfynd/A 48882-2025 artfynd.xlsx
+++ b/artfynd/A 48882-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128962204</v>
       </c>
       <c r="B2" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128962188</v>
       </c>
       <c r="B3" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48882-2025 artfynd.xlsx
+++ b/artfynd/A 48882-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128962204</v>
       </c>
       <c r="B2" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128962188</v>
       </c>
       <c r="B3" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48882-2025 artfynd.xlsx
+++ b/artfynd/A 48882-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128962204</v>
       </c>
       <c r="B2" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128962188</v>
       </c>
       <c r="B3" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48882-2025 artfynd.xlsx
+++ b/artfynd/A 48882-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128962204</v>
       </c>
       <c r="B2" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128962188</v>
       </c>
       <c r="B3" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48882-2025 artfynd.xlsx
+++ b/artfynd/A 48882-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128962204</v>
       </c>
       <c r="B2" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128962188</v>
       </c>
       <c r="B3" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48882-2025 artfynd.xlsx
+++ b/artfynd/A 48882-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128962204</v>
       </c>
       <c r="B2" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128962188</v>
       </c>
       <c r="B3" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48882-2025 artfynd.xlsx
+++ b/artfynd/A 48882-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128962204</v>
       </c>
       <c r="B2" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128962188</v>
       </c>
       <c r="B3" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48882-2025 artfynd.xlsx
+++ b/artfynd/A 48882-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>128962188</v>
       </c>
       <c r="B3" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,14 +805,10 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>

--- a/artfynd/A 48882-2025 artfynd.xlsx
+++ b/artfynd/A 48882-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128962204</v>
       </c>
       <c r="B2" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128962188</v>
       </c>
       <c r="B3" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48882-2025 artfynd.xlsx
+++ b/artfynd/A 48882-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128962204</v>
       </c>
       <c r="B2" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128962188</v>
       </c>
       <c r="B3" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48882-2025 artfynd.xlsx
+++ b/artfynd/A 48882-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128962204</v>
       </c>
       <c r="B2" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128962188</v>
       </c>
       <c r="B3" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48882-2025 artfynd.xlsx
+++ b/artfynd/A 48882-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128962204</v>
       </c>
       <c r="B2" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128962188</v>
       </c>
       <c r="B3" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48882-2025 artfynd.xlsx
+++ b/artfynd/A 48882-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -889,6 +889,212 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129908222</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91619</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Valbergstjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>788341</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7115349</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129908234</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91595</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Valbergstjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>788221</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7115561</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 48882-2025 artfynd.xlsx
+++ b/artfynd/A 48882-2025 artfynd.xlsx
@@ -894,7 +894,7 @@
         <v>129908222</v>
       </c>
       <c r="B4" t="n">
-        <v>91619</v>
+        <v>91622</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>129908234</v>
       </c>
       <c r="B5" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 48882-2025 artfynd.xlsx
+++ b/artfynd/A 48882-2025 artfynd.xlsx
@@ -894,7 +894,7 @@
         <v>129908222</v>
       </c>
       <c r="B4" t="n">
-        <v>91622</v>
+        <v>91625</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>129908234</v>
       </c>
       <c r="B5" t="n">
-        <v>91598</v>
+        <v>91601</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 48882-2025 artfynd.xlsx
+++ b/artfynd/A 48882-2025 artfynd.xlsx
@@ -894,7 +894,7 @@
         <v>129908222</v>
       </c>
       <c r="B4" t="n">
-        <v>91625</v>
+        <v>91626</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>129908234</v>
       </c>
       <c r="B5" t="n">
-        <v>91601</v>
+        <v>91602</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 48882-2025 artfynd.xlsx
+++ b/artfynd/A 48882-2025 artfynd.xlsx
@@ -894,7 +894,7 @@
         <v>129908222</v>
       </c>
       <c r="B4" t="n">
-        <v>91626</v>
+        <v>91643</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>129908234</v>
       </c>
       <c r="B5" t="n">
-        <v>91602</v>
+        <v>91619</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 48882-2025 artfynd.xlsx
+++ b/artfynd/A 48882-2025 artfynd.xlsx
@@ -894,7 +894,7 @@
         <v>129908222</v>
       </c>
       <c r="B4" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>129908234</v>
       </c>
       <c r="B5" t="n">
-        <v>91635</v>
+        <v>91637</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 48882-2025 artfynd.xlsx
+++ b/artfynd/A 48882-2025 artfynd.xlsx
@@ -894,7 +894,7 @@
         <v>129908222</v>
       </c>
       <c r="B4" t="n">
-        <v>91661</v>
+        <v>91748</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>129908234</v>
       </c>
       <c r="B5" t="n">
-        <v>91637</v>
+        <v>91724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 48882-2025 artfynd.xlsx
+++ b/artfynd/A 48882-2025 artfynd.xlsx
@@ -894,7 +894,7 @@
         <v>129908222</v>
       </c>
       <c r="B4" t="n">
-        <v>91748</v>
+        <v>91661</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>129908234</v>
       </c>
       <c r="B5" t="n">
-        <v>91724</v>
+        <v>91637</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 48882-2025 artfynd.xlsx
+++ b/artfynd/A 48882-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129908234</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -887,8 +897,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128962204</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>